--- a/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Triphammer_20260515.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>10.25</v>
       </c>
       <c r="E8" t="n">
-        <v>10.25</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="9">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>23.75</v>
       </c>
       <c r="E9" t="n">
-        <v>71.25</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="10">
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>10.25</v>
       </c>
       <c r="E12" t="n">
-        <v>20.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
